--- a/reports/il_model_deck_selection.xlsx
+++ b/reports/il_model_deck_selection.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checkpoints" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Model screen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Separation (deck)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Model x Deck" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Familiarity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Separation (model)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Fallback" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Local leaderboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Checkpoints" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Model screen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Separation (deck)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Model x Deck" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Familiarity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Separation (model)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Fallback" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,12 +58,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +91,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,6 +457,1392 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Local leaderboard - every agent on one pooled Glicko scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Challengers never play each other; they are linked through the shared 8-agent pool. Two agents are only different when rating +/- 1.96*RD does not overlap. The 'ladder' column is the agent's REAL Kaggle score where one is known -- compare it to the local rating, not to other local ratings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Glicko</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>GXE%</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>real ladder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1877.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[1818, 1936]</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>81</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1841.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[1783, 1900]</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1826.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[1747, 1906]</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1813.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>41</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[1734, 1894]</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1799.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[1741, 1859]</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>76</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1788.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[1708, 1868]</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1788.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>41</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[1708, 1868]</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1757.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[1699, 1817]</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1743.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>41</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[1663, 1823]</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1717.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>41</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[1638, 1798]</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1711.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>41</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[1631, 1791]</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1704.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>41</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[1625, 1785]</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1698.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>41</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[1619, 1778]</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>tb_archaludon</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1685.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[1627, 1745]</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1196.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>romanrozen_strong_start</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1665.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[1607, 1724]</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>makthanithin_1084_baseline</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1655.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[1596, 1714]</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1084.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1653.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>41</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[1574, 1734]</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>improved_prob_main</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1640.9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[1561, 1721]</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>701.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1634.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>41</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[1555, 1714]</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>wmh_alakazam</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1633.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[1575, 1692]</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>860.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>wmh_megastarmie</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1621.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>41</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[1542, 1702]</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>871.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>agent_core_improved</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1602.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>41</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>[1523, 1682]</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>tb_dragapult</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1583.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>[1525, 1642]</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>58</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>880.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1551.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>41</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>[1471, 1631]</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1532</v>
+      </c>
+      <c r="D29" t="n">
+        <v>41</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[1452, 1612]</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>wmh_garchomp</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>1520.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>[1462, 1580]</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>52</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>713.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>tb_alakazam</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>41</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>[1426, 1586]</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>rule_baseline</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1493.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>41</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>[1414, 1574]</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1487.2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>41</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[1407, 1567]</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>tb_rulecore</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1371.9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>41</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>[1292, 1452]</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>38</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>535.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>tb_search</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1320.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>41</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[1241, 1401]</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>660.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>wmh_typhlosion</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>1307.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>41</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>[1228, 1388]</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>1282.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>41</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[1202, 1362]</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>mcts_il_agent</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1256.7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>41</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>[1177, 1337]</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>wmh_bellibolt</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>1231.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>41</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[1151, 1311]</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>grunt</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>1192.7</v>
+      </c>
+      <c r="D40" t="n">
+        <v>41</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[1113, 1273]</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>tb_starmie</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D41" t="n">
+        <v>41</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>[1055, 1215]</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>tb_heuristic</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>1103.9</v>
+      </c>
+      <c r="D42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[1045, 1163]</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>random_legal</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>1045.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[987, 1104]</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Spearman rho (local Glicko vs real ladder) = +0.803  (n=16, permutation p=0.0004)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -725,7 +2112,7 @@
       <c r="G9" t="n">
         <v>0.63656</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>0.16304</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -829,7 +2216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1653,7 +3040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1720,7 +3107,7 @@
       <c r="C5" t="n">
         <v>4.4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1740,7 +3127,7 @@
       <c r="C6" t="n">
         <v>6.9</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1760,7 +3147,7 @@
       <c r="C7" t="n">
         <v>7.5</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1780,7 +3167,7 @@
       <c r="C8" t="n">
         <v>8.1</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1800,7 +3187,7 @@
       <c r="C9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1820,7 +3207,7 @@
       <c r="C10" t="n">
         <v>13.1</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1840,7 +3227,7 @@
       <c r="C11" t="n">
         <v>15</v>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -1860,7 +3247,7 @@
       <c r="C12" t="n">
         <v>23.1</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -1880,7 +3267,7 @@
       <c r="C13" t="n">
         <v>25</v>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -1900,7 +3287,7 @@
       <c r="C14" t="n">
         <v>29.4</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -1920,7 +3307,7 @@
       <c r="C15" t="n">
         <v>49.4</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -1940,7 +3327,7 @@
       <c r="C16" t="n">
         <v>2.5</v>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1960,7 +3347,7 @@
       <c r="C17" t="n">
         <v>3.1</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -1980,7 +3367,7 @@
       <c r="C18" t="n">
         <v>3.8</v>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2000,7 +3387,7 @@
       <c r="C19" t="n">
         <v>4.4</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2020,7 +3407,7 @@
       <c r="C20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2040,7 +3427,7 @@
       <c r="C21" t="n">
         <v>10.6</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2060,7 +3447,7 @@
       <c r="C22" t="n">
         <v>18.8</v>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2080,7 +3467,7 @@
       <c r="C23" t="n">
         <v>20.6</v>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2100,7 +3487,7 @@
       <c r="C24" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2120,7 +3507,7 @@
       <c r="C25" t="n">
         <v>45</v>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2140,7 +3527,7 @@
       <c r="C26" t="n">
         <v>0.6</v>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2160,7 +3547,7 @@
       <c r="C27" t="n">
         <v>1.2</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2180,7 +3567,7 @@
       <c r="C28" t="n">
         <v>1.9</v>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2200,7 +3587,7 @@
       <c r="C29" t="n">
         <v>6.2</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2220,7 +3607,7 @@
       <c r="C30" t="n">
         <v>8.1</v>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2240,7 +3627,7 @@
       <c r="C31" t="n">
         <v>16.2</v>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2260,7 +3647,7 @@
       <c r="C32" t="n">
         <v>18.1</v>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2280,7 +3667,7 @@
       <c r="C33" t="n">
         <v>22.5</v>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2300,7 +3687,7 @@
       <c r="C34" t="n">
         <v>42.5</v>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2320,7 +3707,7 @@
       <c r="C35" t="n">
         <v>0.6</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2340,7 +3727,7 @@
       <c r="C36" t="n">
         <v>1.2</v>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2360,7 +3747,7 @@
       <c r="C37" t="n">
         <v>5.6</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2380,7 +3767,7 @@
       <c r="C38" t="n">
         <v>7.5</v>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2400,7 +3787,7 @@
       <c r="C39" t="n">
         <v>15.6</v>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2420,7 +3807,7 @@
       <c r="C40" t="n">
         <v>17.5</v>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2440,7 +3827,7 @@
       <c r="C41" t="n">
         <v>21.9</v>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2460,7 +3847,7 @@
       <c r="C42" t="n">
         <v>41.9</v>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2480,7 +3867,7 @@
       <c r="C43" t="n">
         <v>0.6</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2500,7 +3887,7 @@
       <c r="C44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2520,7 +3907,7 @@
       <c r="C45" t="n">
         <v>6.9</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2540,7 +3927,7 @@
       <c r="C46" t="n">
         <v>15</v>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2560,7 +3947,7 @@
       <c r="C47" t="n">
         <v>16.9</v>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2580,7 +3967,7 @@
       <c r="C48" t="n">
         <v>21.2</v>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2600,7 +3987,7 @@
       <c r="C49" t="n">
         <v>41.2</v>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2620,7 +4007,7 @@
       <c r="C50" t="n">
         <v>4.4</v>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2640,7 +4027,7 @@
       <c r="C51" t="n">
         <v>6.2</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2660,7 +4047,7 @@
       <c r="C52" t="n">
         <v>14.4</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2680,7 +4067,7 @@
       <c r="C53" t="n">
         <v>16.2</v>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2700,7 +4087,7 @@
       <c r="C54" t="n">
         <v>20.6</v>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2720,7 +4107,7 @@
       <c r="C55" t="n">
         <v>40.6</v>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2740,7 +4127,7 @@
       <c r="C56" t="n">
         <v>1.9</v>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2760,7 +4147,7 @@
       <c r="C57" t="n">
         <v>10</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2780,7 +4167,7 @@
       <c r="C58" t="n">
         <v>11.9</v>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2800,7 +4187,7 @@
       <c r="C59" t="n">
         <v>16.2</v>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2820,7 +4207,7 @@
       <c r="C60" t="n">
         <v>36.2</v>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2840,7 +4227,7 @@
       <c r="C61" t="n">
         <v>8.1</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2860,7 +4247,7 @@
       <c r="C62" t="n">
         <v>10</v>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2880,7 +4267,7 @@
       <c r="C63" t="n">
         <v>14.4</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2900,7 +4287,7 @@
       <c r="C64" t="n">
         <v>34.4</v>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2920,7 +4307,7 @@
       <c r="C65" t="n">
         <v>1.9</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2940,7 +4327,7 @@
       <c r="C66" t="n">
         <v>6.2</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -2960,7 +4347,7 @@
       <c r="C67" t="n">
         <v>26.2</v>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -2980,7 +4367,7 @@
       <c r="C68" t="n">
         <v>4.4</v>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3000,7 +4387,7 @@
       <c r="C69" t="n">
         <v>24.4</v>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -3020,7 +4407,7 @@
       <c r="C70" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -3034,7 +4421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3362,7 +4749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3422,7 +4809,7 @@
       <c r="B5" t="n">
         <v>3488</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3437,7 +4824,7 @@
       <c r="B6" t="n">
         <v>1542</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3452,7 +4839,7 @@
       <c r="B7" t="n">
         <v>784</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3467,7 +4854,7 @@
       <c r="B8" t="n">
         <v>625</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3482,7 +4869,7 @@
       <c r="B9" t="n">
         <v>600</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3497,7 +4884,7 @@
       <c r="B10" t="n">
         <v>318</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -3512,7 +4899,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>NO - unmeasured</t>
         </is>
@@ -3526,7 +4913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3593,7 +4980,7 @@
       <c r="C5" t="n">
         <v>3.4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3613,7 +5000,7 @@
       <c r="C6" t="n">
         <v>4.7</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3633,7 +5020,7 @@
       <c r="C7" t="n">
         <v>5.9</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3653,7 +5040,7 @@
       <c r="C8" t="n">
         <v>7.5</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3673,7 +5060,7 @@
       <c r="C9" t="n">
         <v>8.4</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3693,7 +5080,7 @@
       <c r="C10" t="n">
         <v>11.6</v>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -3713,7 +5100,7 @@
       <c r="C11" t="n">
         <v>1.2</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3733,7 +5120,7 @@
       <c r="C12" t="n">
         <v>2.5</v>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3753,7 +5140,7 @@
       <c r="C13" t="n">
         <v>4.1</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3773,7 +5160,7 @@
       <c r="C14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3793,7 +5180,7 @@
       <c r="C15" t="n">
         <v>8.1</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3813,7 +5200,7 @@
       <c r="C16" t="n">
         <v>1.2</v>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3833,7 +5220,7 @@
       <c r="C17" t="n">
         <v>2.8</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3853,7 +5240,7 @@
       <c r="C18" t="n">
         <v>3.8</v>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3873,7 +5260,7 @@
       <c r="C19" t="n">
         <v>6.9</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3893,7 +5280,7 @@
       <c r="C20" t="n">
         <v>1.6</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3913,7 +5300,7 @@
       <c r="C21" t="n">
         <v>2.5</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3933,7 +5320,7 @@
       <c r="C22" t="n">
         <v>5.6</v>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3953,7 +5340,7 @@
       <c r="C23" t="n">
         <v>0.9</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3973,7 +5360,7 @@
       <c r="C24" t="n">
         <v>4.1</v>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -3993,7 +5380,7 @@
       <c r="C25" t="n">
         <v>3.1</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>not separated</t>
         </is>
@@ -4007,7 +5394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4077,7 +5464,7 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -4098,7 +5485,7 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -4119,7 +5506,7 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -4140,7 +5527,7 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -4161,7 +5548,7 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -4182,7 +5569,7 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="inlineStr">

--- a/reports/il_model_deck_selection.xlsx
+++ b/reports/il_model_deck_selection.xlsx
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>804</v>
+        <v>685.3</v>
       </c>
     </row>
     <row r="27">
@@ -1321,10 +1321,8 @@
           <t>challenger</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H28" s="5" t="n">
+        <v>422.8</v>
       </c>
     </row>
     <row r="29">
@@ -1651,10 +1649,8 @@
           <t>challenger</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H38" s="5" t="n">
+        <v>291.4</v>
       </c>
     </row>
     <row r="39">
@@ -1825,7 +1821,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Spearman rho (local Glicko vs real ladder) = +0.803  (n=16, permutation p=0.0004)</t>
+          <t>Spearman rho vs ladder: +0.765 (n=18, p=0.0004) on ALL anchors -- but 14 of 18 are self-reported by their authors, NOT verified. On the 4 we read ourselves: rho = +1.000 (n=4, p=0.087). agent_core_improved corrected 804.0 -&gt; 685.3 (mean of 4 settled same-build resubmits).</t>
         </is>
       </c>
     </row>

--- a/reports/il_model_deck_selection.xlsx
+++ b/reports/il_model_deck_selection.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -669,18 +669,18 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1799.8</v>
+        <v>1800.9</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[1741, 1859]</t>
+          <t>[1721, 1881]</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -703,22 +703,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1788.1</v>
+        <v>1799.8</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[1708, 1868]</t>
+          <t>[1741, 1859]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>75.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -771,22 +771,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1757.9</v>
+        <v>1788.1</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[1699, 1817]</t>
+          <t>[1708, 1868]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>72.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -805,22 +805,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1743.3</v>
+        <v>1757.9</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[1663, 1823]</t>
+          <t>[1699, 1817]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>71.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1717.7</v>
+        <v>1743.3</v>
       </c>
       <c r="D14" t="n">
         <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[1638, 1798]</t>
+          <t>[1663, 1823]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>69.7</v>
+        <v>71.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -873,22 +873,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1711.3</v>
+        <v>1717.7</v>
       </c>
       <c r="D15" t="n">
         <v>41</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[1631, 1791]</t>
+          <t>[1638, 1798]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -907,22 +907,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@alakazam</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1704.9</v>
+        <v>1711.3</v>
       </c>
       <c r="D16" t="n">
         <v>41</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[1625, 1785]</t>
+          <t>[1631, 1791]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -941,22 +941,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1698.5</v>
+        <v>1704.9</v>
       </c>
       <c r="D17" t="n">
         <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[1619, 1778]</t>
+          <t>[1625, 1785]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68.2</v>
+        <v>68.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -975,30 +975,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>tb_archaludon</t>
+          <t>il_alldays_3ep@alakazam</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1685.9</v>
+        <v>1698.5</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[1627, 1745]</t>
+          <t>[1619, 1778]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>67.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pool</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>1196.1</v>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1007,22 +1009,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>romanrozen_strong_start</t>
+          <t>tb_archaludon</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1665.5</v>
+        <v>1684.5</v>
       </c>
       <c r="D19" t="n">
         <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[1607, 1724]</t>
+          <t>[1626, 1743]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>65.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1030,7 +1032,7 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>950</v>
+        <v>1196.1</v>
       </c>
     </row>
     <row r="20">
@@ -1039,22 +1041,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>makthanithin_1084_baseline</t>
+          <t>romanrozen_strong_start</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1655.3</v>
+        <v>1665.2</v>
       </c>
       <c r="D20" t="n">
         <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[1596, 1714]</t>
+          <t>[1606, 1724]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1062,7 +1064,7 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1084.5</v>
+        <v>950</v>
       </c>
     </row>
     <row r="21">
@@ -1105,30 +1107,30 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>improved_prob_main</t>
+          <t>makthanithin_1084_baseline</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1640.9</v>
+        <v>1653.4</v>
       </c>
       <c r="D22" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[1561, 1721]</t>
+          <t>[1595, 1712]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>63.2</v>
+        <v>64.3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>challenger</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>701.6</v>
+        <v>1084.5</v>
       </c>
     </row>
     <row r="23">
@@ -1137,32 +1139,30 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>improved_prob_main</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1634.5</v>
+        <v>1640.9</v>
       </c>
       <c r="D23" t="n">
         <v>41</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[1555, 1714]</t>
+          <t>[1561, 1721]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>62.6</v>
+        <v>63.2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H23" s="5" t="n">
+        <v>701.6</v>
       </c>
     </row>
     <row r="24">
@@ -1175,18 +1175,18 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1633.5</v>
+        <v>1634.9</v>
       </c>
       <c r="D24" t="n">
         <v>30</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[1575, 1692]</t>
+          <t>[1576, 1694]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1203,30 +1203,32 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>wmh_megastarmie</t>
+          <t>il_small_comb_2ep@alakazam</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1621.7</v>
+        <v>1634.5</v>
       </c>
       <c r="D25" t="n">
         <v>41</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[1542, 1702]</t>
+          <t>[1555, 1714]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>61.5</v>
+        <v>62.6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>871.5</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1235,22 +1237,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>agent_core_improved</t>
+          <t>wmh_megastarmie</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1602.4</v>
+        <v>1621.7</v>
       </c>
       <c r="D26" t="n">
         <v>41</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[1523, 1682]</t>
+          <t>[1542, 1702]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>59.7</v>
+        <v>61.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1258,7 +1260,7 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>685.3</v>
+        <v>871.5</v>
       </c>
     </row>
     <row r="27">
@@ -1267,30 +1269,30 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>tb_dragapult</t>
+          <t>agent_core_improved</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1583.6</v>
+        <v>1602.4</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[1525, 1642]</t>
+          <t>[1523, 1682]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>58</v>
+        <v>59.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>pool</t>
+          <t>challenger</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>880.9</v>
+        <v>685.3</v>
       </c>
     </row>
     <row r="28">
@@ -1299,30 +1301,30 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>tb_dragapult</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1551.2</v>
+        <v>1584.7</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[1471, 1631]</t>
+          <t>[1526, 1644]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>54.9</v>
+        <v>58.1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>challenger</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>422.8</v>
+        <v>880.9</v>
       </c>
     </row>
     <row r="29">
@@ -1331,22 +1333,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1532</v>
+        <v>1570.4</v>
       </c>
       <c r="D29" t="n">
         <v>41</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[1452, 1612]</t>
+          <t>[1491, 1650]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>53.1</v>
+        <v>56.7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1365,30 +1367,30 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>wmh_garchomp</t>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1520.9</v>
+        <v>1551.2</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[1462, 1580]</t>
+          <t>[1471, 1631]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>54.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pool</t>
+          <t>challenger</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>713.8</v>
+        <v>422.8</v>
       </c>
     </row>
     <row r="31">
@@ -1397,30 +1399,32 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>tb_alakazam</t>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1506.4</v>
+        <v>1532</v>
       </c>
       <c r="D31" t="n">
         <v>41</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[1426, 1586]</t>
+          <t>[1452, 1612]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>50.6</v>
+        <v>53.1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>659</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1429,32 +1433,30 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>rule_baseline</t>
+          <t>wmh_garchomp</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1493.6</v>
+        <v>1518.8</v>
       </c>
       <c r="D32" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[1414, 1574]</t>
+          <t>[1460, 1578]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>49.4</v>
+        <v>51.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>challenger</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>713.8</v>
       </c>
     </row>
     <row r="33">
@@ -1463,32 +1465,30 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>tb_alakazam</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1487.2</v>
+        <v>1506.4</v>
       </c>
       <c r="D33" t="n">
         <v>41</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[1407, 1567]</t>
+          <t>[1426, 1586]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>48.8</v>
+        <v>50.6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>659</v>
       </c>
     </row>
     <row r="34">
@@ -1497,30 +1497,32 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>tb_rulecore</t>
+          <t>rule_baseline</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1371.9</v>
+        <v>1493.6</v>
       </c>
       <c r="D34" t="n">
         <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[1292, 1452]</t>
+          <t>[1414, 1574]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>49.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>535.6</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1529,30 +1531,32 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>tb_search</t>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1320.7</v>
+        <v>1487.2</v>
       </c>
       <c r="D35" t="n">
         <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[1241, 1401]</t>
+          <t>[1407, 1567]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>33.4</v>
+        <v>48.8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>660.5</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1561,22 +1565,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>wmh_typhlosion</t>
+          <t>tb_rulecore</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1307.9</v>
+        <v>1371.9</v>
       </c>
       <c r="D36" t="n">
         <v>41</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[1228, 1388]</t>
+          <t>[1292, 1452]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>32.4</v>
+        <v>38</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1584,7 +1588,7 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>532</v>
+        <v>535.6</v>
       </c>
     </row>
     <row r="37">
@@ -1593,32 +1597,30 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>tb_search</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1282.3</v>
+        <v>1320.7</v>
       </c>
       <c r="D37" t="n">
         <v>41</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[1202, 1362]</t>
+          <t>[1241, 1401]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>30.3</v>
+        <v>33.4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>660.5</v>
       </c>
     </row>
     <row r="38">
@@ -1627,22 +1629,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>mcts_il_agent</t>
+          <t>wmh_typhlosion</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1256.7</v>
+        <v>1307.9</v>
       </c>
       <c r="D38" t="n">
         <v>41</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[1177, 1337]</t>
+          <t>[1228, 1388]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28.2</v>
+        <v>32.4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1650,7 +1652,7 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>291.4</v>
+        <v>532</v>
       </c>
     </row>
     <row r="39">
@@ -1659,30 +1661,32 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>wmh_bellibolt</t>
+          <t>il_bc_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1231.1</v>
+        <v>1282.3</v>
       </c>
       <c r="D39" t="n">
         <v>41</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[1151, 1311]</t>
+          <t>[1202, 1362]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>26.3</v>
+        <v>30.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
-        <v>836</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1691,32 +1695,30 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>grunt</t>
+          <t>mcts_il_agent</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1192.7</v>
+        <v>1256.7</v>
       </c>
       <c r="D40" t="n">
         <v>41</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[1113, 1273]</t>
+          <t>[1177, 1337]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.5</v>
+        <v>28.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>291.4</v>
       </c>
     </row>
     <row r="41">
@@ -1725,22 +1727,22 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>tb_starmie</t>
+          <t>wmh_bellibolt</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1135</v>
+        <v>1231.1</v>
       </c>
       <c r="D41" t="n">
         <v>41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[1055, 1215]</t>
+          <t>[1151, 1311]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>19.8</v>
+        <v>26.3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1748,7 +1750,7 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>277.5</v>
+        <v>836</v>
       </c>
     </row>
     <row r="42">
@@ -1757,30 +1759,32 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>tb_heuristic</t>
+          <t>grunt</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1103.9</v>
+        <v>1192.7</v>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[1045, 1163]</t>
+          <t>[1113, 1273]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>17.9</v>
+        <v>23.5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>pool</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>633</v>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1789,37 +1793,101 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>tb_starmie</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D43" t="n">
+        <v>41</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[1055, 1215]</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>tb_heuristic</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>1102.9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[1044, 1162]</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>random_legal</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C45" s="4" t="n">
         <v>1045.6</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D45" t="n">
         <v>30</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>[987, 1104]</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>14.8</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>pool</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Spearman rho vs ladder: +0.765 (n=18, p=0.0004) on ALL anchors -- but 14 of 18 are self-reported by their authors, NOT verified. On the 4 we read ourselves: rho = +1.000 (n=4, p=0.087). agent_core_improved corrected 804.0 -&gt; 685.3 (mean of 4 settled same-build resubmits).</t>
         </is>
@@ -3042,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3092,16 +3160,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -3112,16 +3180,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -3132,16 +3200,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -3152,16 +3220,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
@@ -3172,16 +3240,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
@@ -3192,16 +3260,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>il_alldays_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
-        </is>
-      </c>
       <c r="C10" t="n">
-        <v>13.1</v>
+        <v>8.4</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -3212,36 +3280,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>8.4</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>11.6</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
@@ -3252,16 +3320,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>12.8</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -3272,16 +3340,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.4</v>
+        <v>15.3</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -3292,16 +3360,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@alakazam</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>49.4</v>
+        <v>15.9</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -3312,136 +3380,136 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>16.6</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_alldays_3ep@alakazam</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>17.2</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>21.6</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_small_comb_2ep@alakazam</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>23.4</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>29.7</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>31.6</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.8</v>
+        <v>33.4</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
@@ -3452,16 +3520,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20.6</v>
+        <v>37.8</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
@@ -3472,16 +3540,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>57.8</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
@@ -3492,36 +3560,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>1.2</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -3532,16 +3600,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
@@ -3552,16 +3620,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
@@ -3572,16 +3640,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
@@ -3592,16 +3660,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -3612,56 +3680,56 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>8.1</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>9.4</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>il_alldays_3ep@team_rockets_spidops</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
-        </is>
-      </c>
       <c r="C33" t="n">
-        <v>22.5</v>
+        <v>11.9</v>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
@@ -3672,16 +3740,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@alakazam</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>42.5</v>
+        <v>12.5</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
@@ -3692,7 +3760,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3701,18 +3769,18 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>13.1</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3721,18 +3789,18 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>13.8</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3741,18 +3809,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>18.1</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3761,27 +3829,27 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>20</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>15.6</v>
+        <v>26.2</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -3792,16 +3860,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.5</v>
+        <v>28.1</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
@@ -3812,16 +3880,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21.9</v>
+        <v>30</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
@@ -3832,16 +3900,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>il_bc_3ep@alakazam</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>41.9</v>
+        <v>34.4</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
@@ -3852,36 +3920,36 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_hfstream_comb_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>54.4</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
@@ -3892,16 +3960,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
@@ -3912,16 +3980,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
@@ -3932,76 +4000,76 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>3.8</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>3.8</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>il_bc_3ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>6.9</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
@@ -4012,16 +4080,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6.2</v>
+        <v>10.6</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
@@ -4032,16 +4100,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@alakazam</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>14.4</v>
+        <v>11.2</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
@@ -4052,56 +4120,56 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_bc_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>11.9</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>il_alldays_3ep@alakazam</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
-        </is>
-      </c>
       <c r="C54" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>12.5</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@alakazam</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>40.6</v>
+        <v>16.9</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
@@ -4112,7 +4180,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4121,67 +4189,67 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>18.8</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>25</v>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>26.9</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>16.2</v>
+        <v>28.8</v>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
@@ -4192,16 +4260,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36.2</v>
+        <v>33.1</v>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
@@ -4212,36 +4280,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_bc_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>not separated</t>
+        <v>53.1</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
@@ -4252,16 +4320,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14.4</v>
+        <v>1.6</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
@@ -4272,36 +4340,36 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>2.5</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
@@ -4312,16 +4380,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
@@ -4332,36 +4400,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>6.9</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
@@ -4372,38 +4440,2918 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@team_rockets_spidops</t>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>il_bc_3ep@mega_lucario_ex</t>
+          <t>il_bc_3ep@alakazam</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>SEPARATED</t>
+        <v>10</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>il_small_comb_2ep@mega_lucario_ex</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C77" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>il_bc_4ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>il_bc_3ep@mega_lucario_ex</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C78" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>15</v>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>25</v>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>15</v>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>25</v>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>10</v>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>25</v>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>45</v>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>5</v>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>15</v>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>10</v>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>10</v>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@alakazam</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>not separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@team_rockets_spidops</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>SEPARATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>il_bc_3ep@mega_lucario_ex</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>20</v>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>SEPARATED</t>
         </is>
@@ -4423,7 +7371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4540,12 +7488,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>il_bc_2ep</t>
+          <t>il_alldays_equalsteps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.1 ± 3.3</t>
+          <t>79.4 ± 3.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4565,83 +7513,83 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56.9 ± 3.9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>il_bc_3ep</t>
+          <t>il_bc_2ep</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>81.9 ± 3.0</t>
+          <t>78.1 ± 3.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>70.6 ± 3.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>70.0 ± 3.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.8 ± 3.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.8 ± 3.6</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>il_bc_4ep</t>
+          <t>il_bc_3ep</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80.6 ± 3.1</t>
+          <t>81.9 ± 3.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70.6 ± 3.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70.0 ± 3.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73.8 ± 3.5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28.8 ± 3.6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>il_hfstream_comb_3ep</t>
+          <t>il_bc_4ep</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>83.1 ± 2.1</t>
+          <t>80.6 ± 3.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4668,12 +7616,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>il_medium_3ep</t>
+          <t>il_hfstream_comb_3ep</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>79.1 ± 2.3</t>
+          <t>83.1 ± 2.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4700,38 +7648,70 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>il_medium_3ep</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>79.1 ± 2.3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>il_small_comb_2ep</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>75.0 ± 2.4</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>63.1 ± 3.8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>53.1 ± 3.9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>65.0 ± 3.8</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>48.8 ± 4.0</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Red = below the 150-episode familiarity floor: unmeasured, not bad.</t>
         </is>

--- a/reports/il_model_deck_selection.xlsx
+++ b/reports/il_model_deck_selection.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -537,18 +537,18 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1877.1</v>
+        <v>1885.4</v>
       </c>
       <c r="D5" t="n">
         <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[1818, 1936]</t>
+          <t>[1827, 1944]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -571,18 +571,18 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1841.7</v>
+        <v>1852.1</v>
       </c>
       <c r="D6" t="n">
         <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[1783, 1900]</t>
+          <t>[1793, 1911]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78.8</v>
+        <v>79.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -605,18 +605,18 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1826.5</v>
+        <v>1847.7</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[1747, 1906]</t>
+          <t>[1772, 1923]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>77.8</v>
+        <v>79.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -639,18 +639,18 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1813.7</v>
+        <v>1836.3</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[1734, 1894]</t>
+          <t>[1761, 1912]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>76.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -673,18 +673,18 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1800.9</v>
+        <v>1824.9</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[1721, 1881]</t>
+          <t>[1750, 1900]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>77.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -703,22 +703,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
+          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1799.8</v>
+        <v>1813.5</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[1741, 1859]</t>
+          <t>[1738, 1889]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -737,22 +737,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@cynthias_garchomp_ex</t>
+          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1788.1</v>
+        <v>1813.5</v>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[1708, 1868]</t>
+          <t>[1738, 1889]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>75.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>il_bc_2ep@marnies_grimmsnarl_ex</t>
+          <t>il_medium_3ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1788.1</v>
+        <v>1812.6</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[1708, 1868]</t>
+          <t>[1754, 1871]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>75.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -805,22 +805,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
+          <t>il_bc_3ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1757.9</v>
+        <v>1773.6</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[1699, 1817]</t>
+          <t>[1698, 1849]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>72.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -839,22 +839,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>il_bc_3ep@cynthias_garchomp_ex</t>
+          <t>il_small_comb_2ep@marnies_grimmsnarl_ex</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1743.3</v>
+        <v>1773.1</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[1663, 1823]</t>
+          <t>[1714, 1832]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>71.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -877,18 +877,18 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1717.7</v>
+        <v>1745.1</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[1638, 1798]</t>
+          <t>[1670, 1821]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>69.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -911,18 +911,18 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1711.3</v>
+        <v>1745.1</v>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[1631, 1791]</t>
+          <t>[1670, 1821]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>69.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -945,18 +945,18 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1704.9</v>
+        <v>1728</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[1625, 1785]</t>
+          <t>[1653, 1803]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -979,18 +979,18 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1698.5</v>
+        <v>1722.3</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[1619, 1778]</t>
+          <t>[1647, 1798]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>68.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1009,30 +1009,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>tb_archaludon</t>
+          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1684.5</v>
+        <v>1688.1</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[1626, 1743]</t>
+          <t>[1613, 1764]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>67.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pool</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>1196.1</v>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1041,22 +1043,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>romanrozen_strong_start</t>
+          <t>tb_archaludon</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1665.2</v>
+        <v>1685.3</v>
       </c>
       <c r="D20" t="n">
         <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[1606, 1724]</t>
+          <t>[1626, 1744]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>65.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1064,7 +1066,7 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>950</v>
+        <v>1196.1</v>
       </c>
     </row>
     <row r="21">
@@ -1073,32 +1075,30 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@cynthias_garchomp_ex</t>
+          <t>improved_prob_main</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1653.7</v>
+        <v>1682.4</v>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[1574, 1734]</t>
+          <t>[1607, 1758]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>64.3</v>
+        <v>66.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H21" s="5" t="n">
+        <v>701.6</v>
       </c>
     </row>
     <row r="22">
@@ -1107,30 +1107,32 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>makthanithin_1084_baseline</t>
+          <t>il_small_comb_2ep@alakazam</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1653.4</v>
+        <v>1671</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[1595, 1712]</t>
+          <t>[1596, 1746]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>64.3</v>
+        <v>65.8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>pool</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1084.5</v>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1139,30 +1141,30 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>improved_prob_main</t>
+          <t>romanrozen_strong_start</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1640.9</v>
+        <v>1666</v>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[1561, 1721]</t>
+          <t>[1607, 1725]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>63.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>challenger</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>701.6</v>
+        <v>950</v>
       </c>
     </row>
     <row r="24">
@@ -1171,30 +1173,30 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>wmh_alakazam</t>
+          <t>wmh_megastarmie</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1634.9</v>
+        <v>1665.3</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[1576, 1694]</t>
+          <t>[1590, 1741]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>62.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pool</t>
+          <t>challenger</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>860.3</v>
+        <v>871.5</v>
       </c>
     </row>
     <row r="25">
@@ -1203,32 +1205,30 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@alakazam</t>
+          <t>makthanithin_1084_baseline</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1634.5</v>
+        <v>1654.4</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[1555, 1714]</t>
+          <t>[1596, 1713]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>62.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>challenger</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1084.5</v>
       </c>
     </row>
     <row r="26">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>wmh_megastarmie</t>
+          <t>agent_core_improved</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1621.7</v>
+        <v>1648.2</v>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[1542, 1702]</t>
+          <t>[1573, 1724]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>61.5</v>
+        <v>63.9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>871.5</v>
+        <v>685.3</v>
       </c>
     </row>
     <row r="27">
@@ -1269,30 +1269,30 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>agent_core_improved</t>
+          <t>wmh_alakazam</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1602.4</v>
+        <v>1635.9</v>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[1523, 1682]</t>
+          <t>[1577, 1695]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>59.7</v>
+        <v>62.8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>challenger</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>685.3</v>
+        <v>860.3</v>
       </c>
     </row>
     <row r="28">
@@ -1301,30 +1301,32 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>tb_dragapult</t>
+          <t>il_alldays_equalsteps@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1584.7</v>
+        <v>1608.3</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[1526, 1644]</t>
+          <t>[1533, 1684]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>58.1</v>
+        <v>60.2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pool</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>880.9</v>
+          <t>challenger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1333,32 +1335,30 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_equalsteps@mega_lucario_ex</t>
+          <t>il_alldays_3ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1570.4</v>
+        <v>1596.9</v>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[1491, 1650]</t>
+          <t>[1521, 1672]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>56.7</v>
+        <v>59.2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H29" s="5" t="n">
+        <v>422.8</v>
       </c>
     </row>
     <row r="30">
@@ -1367,30 +1367,30 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>il_alldays_3ep@mega_lucario_ex</t>
+          <t>tb_dragapult</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1551.2</v>
+        <v>1585.8</v>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[1471, 1631]</t>
+          <t>[1527, 1645]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>54.9</v>
+        <v>58.2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>challenger</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>422.8</v>
+        <v>880.9</v>
       </c>
     </row>
     <row r="31">
@@ -1403,18 +1403,18 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1532</v>
+        <v>1568.4</v>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[1452, 1612]</t>
+          <t>[1493, 1644]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>53.1</v>
+        <v>56.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1433,30 +1433,30 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>wmh_garchomp</t>
+          <t>tb_alakazam</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1518.8</v>
+        <v>1539.9</v>
       </c>
       <c r="D32" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[1460, 1578]</t>
+          <t>[1464, 1615]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>51.8</v>
+        <v>53.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>pool</t>
+          <t>challenger</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>713.8</v>
+        <v>659</v>
       </c>
     </row>
     <row r="33">
@@ -1465,30 +1465,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>tb_alakazam</t>
+          <t>il_small_comb_2ep@mega_lucario_ex</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1506.4</v>
+        <v>1522.8</v>
       </c>
       <c r="D33" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[1426, 1586]</t>
+          <t>[1447, 1598]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>50.6</v>
+        <v>52.2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>challenger</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>659</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1497,32 +1499,30 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>rule_baseline</t>
+          <t>wmh_garchomp</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1493.6</v>
+        <v>1520.1</v>
       </c>
       <c r="D34" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[1414, 1574]</t>
+          <t>[1461, 1579]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>49.4</v>
+        <v>51.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>challenger</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>713.8</v>
       </c>
     </row>
     <row r="35">
@@ -1531,22 +1531,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>il_small_comb_2ep@mega_lucario_ex</t>
+          <t>rule_baseline</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1487.2</v>
+        <v>1511.4</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[1407, 1567]</t>
+          <t>[1436, 1587]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1569,18 +1569,18 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1371.9</v>
+        <v>1414.5</v>
       </c>
       <c r="D36" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[1292, 1452]</t>
+          <t>[1339, 1490]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>38</v>
+        <v>41.9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1601,18 +1601,18 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1320.7</v>
+        <v>1351.8</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[1241, 1401]</t>
+          <t>[1276, 1427]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>33.4</v>
+        <v>36.1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1633,18 +1633,18 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1307.9</v>
+        <v>1346.1</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[1228, 1388]</t>
+          <t>[1271, 1421]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>32.4</v>
+        <v>35.6</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1665,18 +1665,18 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1282.3</v>
+        <v>1311.9</v>
       </c>
       <c r="D39" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[1202, 1362]</t>
+          <t>[1236, 1387]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>30.3</v>
+        <v>32.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1699,18 +1699,18 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1256.7</v>
+        <v>1306.2</v>
       </c>
       <c r="D40" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[1177, 1337]</t>
+          <t>[1231, 1382]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>28.2</v>
+        <v>32.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1731,14 +1731,14 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1231.1</v>
+        <v>1232.1</v>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[1151, 1311]</t>
+          <t>[1157, 1307]</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1763,18 +1763,18 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1192.7</v>
+        <v>1203.6</v>
       </c>
       <c r="D42" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[1113, 1273]</t>
+          <t>[1128, 1279]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1793,30 +1793,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>tb_starmie</t>
+          <t>wmh_grimmsnarl</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1135</v>
+        <v>1176</v>
       </c>
       <c r="D43" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[1055, 1215]</t>
+          <t>[1117, 1235]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>challenger</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>277.5</v>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1825,30 +1827,30 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>tb_heuristic</t>
+          <t>tb_starmie</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1102.9</v>
+        <v>1146.6</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[1044, 1162]</t>
+          <t>[1071, 1222]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>17.9</v>
+        <v>20.5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>pool</t>
+          <t>challenger</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>633</v>
+        <v>277.5</v>
       </c>
     </row>
     <row r="45">
@@ -1857,37 +1859,69 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>random_legal</t>
+          <t>tb_heuristic</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1045.6</v>
+        <v>1102.6</v>
       </c>
       <c r="D45" t="n">
         <v>30</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[987, 1104]</t>
+          <t>[1044, 1161]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>14.8</v>
+        <v>17.8</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>pool</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="5" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>random_legal</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>1045.9</v>
+      </c>
+      <c r="D46" t="n">
+        <v>30</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>[987, 1105]</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>pool</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Spearman rho vs ladder: +0.765 (n=18, p=0.0004) on ALL anchors -- but 14 of 18 are self-reported by their authors, NOT verified. On the 4 we read ourselves: rho = +1.000 (n=4, p=0.087). agent_core_improved corrected 804.0 -&gt; 685.3 (mean of 4 settled same-build resubmits).</t>
         </is>
